--- a/pipeline_output/UP_UK_2W_H&M.xlsx
+++ b/pipeline_output/UP_UK_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11278,12 +11278,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11522,12 +11522,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11893,12 +11893,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -12020,12 +12020,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12137,12 +12137,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12645,12 +12645,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12996,12 +12996,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13113,12 +13113,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13230,12 +13230,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13611,12 +13611,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13855,12 +13855,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14109,12 +14109,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14226,12 +14226,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14480,12 +14480,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14597,12 +14597,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14851,12 +14851,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14978,12 +14978,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15232,12 +15232,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15613,12 +15613,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16218,12 +16218,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16335,12 +16335,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16452,12 +16452,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16569,12 +16569,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16803,12 +16803,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16920,12 +16920,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17037,12 +17037,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17154,12 +17154,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17271,12 +17271,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17739,12 +17739,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
